--- a/data/flat/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/flat/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ86"/>
+  <dimension ref="A1:AJ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10026,8 +10026,9230 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ddce2cf599e64e14</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182185</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.855057</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.015056999999999987</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.097244Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>57d51729a22745df</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182173</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.69013</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.8098859315589353</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>-0.11975593155893527</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:05.043465Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2ece48dd4cf34f36</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182175</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.600871</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.030055549356223232</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:05.339292Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>c9a7638bbf04454e</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182182</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.745582</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>-0.13436998079231688</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:04.034895Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>0d4e135546ce49e0</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182207</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.533657</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.023853078431372632</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:05.887542Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>8aa9c455940e443e</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182166</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.771595</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.7802197802197802</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>-0.008624780219780193</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:08.588851Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>c854733ccbb742d0</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182194</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.886886</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.9500000000000001</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>-0.06311400000000011</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:06.998289Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>33edf7fb727d4dff</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182202</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.623502</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.18297336563876654</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:06.679525Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>b7733c53457f4d5b</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182203</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.660541</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>-0.05934695518207278</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:09.186654Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>3a09a8af6e9c4312</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182167</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.605938</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>-0.0034370000000000234</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:10.560775Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>51243e3064634326</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182168</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.66176</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>0.001896054421768656</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:09.718459Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>e2cebe7902a84d34</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182188</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.540992</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.010475568075117403</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:11.148633Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:30Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2379b48e38104222</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182199</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.939322</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.9500000000000001</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>-0.010678000000000076</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:11.539120Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ba481b356a0e400f</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182187</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.669885</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.7297297297297298</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>-0.05984472972972987</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:12.090033Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:30Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>a974bcb77d734662</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182094</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.589516</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.14898736563876658</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.024816Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>1f74556b91c64f8d</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182089</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.60078</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>-0.02884962962962956</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:02.903280Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>4cc4b7ba762c4eeb</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182083</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.548768</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>0.058571921568627505</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:02.853017Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>aadae8ba0eb54c56</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182091</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.601999</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.8299319727891156</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>-0.22793297278911562</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:02.967788Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>6951f9707b184313</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182092</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.511713</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.011712999999999973</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:02.978276Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>4b68891ff41e46eb</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182088</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.578623</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.06881907843137258</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.076813Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>f4053c518d794bd6</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182082</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.523723</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>-0.1567881821086261</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.073966Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>640eac7b90a64e5f</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182093</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.627805</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.2977719966996699</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.126714Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>84fb10f39c604e91</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182096</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.534715</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>-0.10557276978417263</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:03.102732Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>22744bde90504b0d</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181808</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.503757</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>-0.11601486311787068</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:14.653874Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>0aa7afe8c8e74995</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181822</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.559835</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.029318568075117346</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:13.463544Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>824c8938fcab409f</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181825</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.568221</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.008749634361233438</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:16.717621Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>7d01906e679847dd</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181831</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.514482</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>-0.11514762962962954</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:15.802200Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2db1627683da472d</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181780</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.533424</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>-0.0373914506437768</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:19.597245Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>25172bc9214e4751</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181813</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.69073</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.10056606557377046</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:20.678564Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>4ea939ec89364762</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181818</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.627342</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>-0.032521945578231404</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:20.050799Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>0a01fca1373f4ce2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181819</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.51802</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.11802000000000001</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:18.537544Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>d04cf63b33854714</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181773</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.734849</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.7601918465227817</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>-0.025342846522781737</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:22.488154Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>3456d69eb4674db6</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181784</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.506379</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>-0.012851769230769139</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:23.167963Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>e9c653efee4a47c0</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181805</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.517974</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>-0.04149736563876649</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:24.613831Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>8c9f380695234bd5</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181810</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.781578</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.11161100330033003</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:24.080033Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>08b49bf2de7540d0</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181829</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.595125</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>-0.024646863117870677</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:21.880736Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>324a868a3a6a43d0</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181776</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.764483</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.8299319727891156</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>-0.06544897278911554</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:26.928036Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>377bcf0047134579</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181778</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.523934</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.11409793442622951</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:26.328209Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>9dbc8c88bec9413c</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181789</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.654828</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0.035056136882129274</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:25.317785Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>15860dfb8fce4f01</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181737</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.843242</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.8699609882964889</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>-0.026718988296488888</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:27.955801Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>68dbb0873cae4725</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181748</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.701855</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.7297297297297298</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>-0.02787472972972982</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:28.418646Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>d570ab74983346f6</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181740</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.583443</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>-0.11625669969969965</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:28.729724Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:30Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2d233c45fd2a4cb4</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181769</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.62292</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.08374949308755764</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:16:28.966922Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:30Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>a6461608316e471b</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182185</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.855057</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.015056999999999987</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.879231Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>8954fd7efba448ca</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182173</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.69013</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.8098859315589353</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>-0.11975593155893527</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:33.928684Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>be293ba508e8469d</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182175</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.600871</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0.030055549356223232</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:34.336934Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>33500a1d302e4d4f</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182182</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.745582</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.8999999999999999</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>-0.15441799999999994</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:32.830493Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>3b3ece690a90446d</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182207</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.533657</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.023853078431372632</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:34.995635Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2815f5eb7a4544ce</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182166</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.771595</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.7802197802197802</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>-0.008624780219780193</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:37.895879Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>85ba48df49f741af</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182194</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.886886</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.9500000000000001</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>-0.06311400000000011</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:36.220323Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2bfc1052bd1e48e9</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182202</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.623502</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.1943174506437768</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:35.666785Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>625d416245cb4671</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182203</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.660541</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>-0.05934695518207278</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:38.783015Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>c14caf71479b49ef</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182167</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.605938</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>-0.0034370000000000234</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:40.069254Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00Z</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>1b30aeb461414d8a</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182168</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.66176</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.001896054421768656</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:39.130120Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00Z</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>3a7a493e0a904ea4</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182188</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.540992</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.0018214930875576352</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:40.814085Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:30Z</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>3f83630b5601464b</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182199</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.939322</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.9500000000000001</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>-0.010678000000000076</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:41.356996Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>b01a75dbb9024ab2</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182187</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.669885</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>-0.05000295518207287</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:42.022758Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:30Z</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>30282e8a35b34107</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182094</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.589516</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.14898736563876658</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.682126Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>b055ffdb2c98438f</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182089</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.60078</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>-0.01899186311787071</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.683641Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>d524bd63a9814238</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182083</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.548768</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.048768000000000034</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.509930Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00Z</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>7ebbf7a4cfec4728</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182091</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.601999</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>-0.23800100000000002</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.401094Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>ca434775c1404fdc</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182092</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.511713</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.011712999999999973</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.615874Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>fd8f7902cead4e62</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182088</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.578623</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.06881907843137258</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.464146Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>ec051af3490d4250</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182082</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.523723</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>-0.1567881821086261</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.722797Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>7e4b9d6dd6364401</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182093</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.627805</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.2977719966996699</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.820806Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>82467c75dc4a44ab</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>961-2026:182096</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.534715</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>-0.09491462962962949</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.801243Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00Z</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>23e9610410954fa2</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181808</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.503757</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>-0.12587262962962953</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:44.778344Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>cfeecb99e79e435f</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181822</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.559835</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.04060423076923081</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:43.563914Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>92131ac881324021</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181825</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.568221</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.01867145045045049</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:46.890318Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>274705eed8b34306</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181831</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.514482</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>-0.11514762962962954</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:45.972655Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00Z</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>7317db45957a4370</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181780</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.533424</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>-0.04640793277310917</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:49.747408Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>4248c6ca7184475c</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181813</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.69073</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.11089806722689077</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:50.946314Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>eccd144103034590</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181818</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.627342</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>-0.032521945578231404</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:50.213634Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>804397d158844d6d</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181819</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.51802</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.11802000000000001</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:48.641413Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>257b4772dd8e4c41</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181773</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.734849</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.7802197802197802</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>-0.04537078021978025</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:52.807217Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>a929ce1d98f44ae3</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181784</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.506379</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>-0.0034249215686273926</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:53.527933Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>8c825ec1792b4978</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181805</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.517974</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>-0.04149736563876649</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:55.134953Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>964f591db84a40f5</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181810</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.781578</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.11161100330033003</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:54.448463Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>5470cbe0b99b43a7</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181829</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.595125</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>-0.024646863117870677</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:52.122317Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>3417f1f98b0a4b16</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181776</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.764483</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.8500749625187406</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>-0.08559196251874057</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:57.596271Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>275c12d713b643f1</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181778</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.523934</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.11409793442622951</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:56.817049Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ef953289ed744c9d</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181789</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.654828</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.035056136882129274</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:55.916912Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30Z</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>b9afe1a6f12946ec</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181737</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.843242</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.88998899889989</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>-0.04674699889988998</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:59.146178Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00Z</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>611114dac4f14755</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181759</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.686447</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>-0.06355299999999997</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:58.246120Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00Z</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>c1ace1b28d2e4a7e</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181748</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.701855</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.07222537037037047</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:59.800144Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>869526e8435d4fce</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181740</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.583443</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.012627549356223233</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:00.632213Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:30Z</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>5c6ba049359a4a53</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181769</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.62292</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.1327239215686275</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:01.150443Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:30Z</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ86"/>
+  <autoFilter ref="A1:AJ173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/flat/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/flat/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$667</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$675</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ667"/>
+  <dimension ref="A1:AJ675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -70460,14 +70460,34 @@
       <c r="W639" s="2" t="inlineStr"/>
       <c r="X639" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y639" s="2" t="inlineStr"/>
-      <c r="Z639" s="2" t="inlineStr"/>
-      <c r="AA639" s="2" t="inlineStr"/>
-      <c r="AB639" s="2" t="inlineStr"/>
-      <c r="AC639" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y639" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z639" s="2" t="inlineStr">
+        <is>
+          <t>0.660000</t>
+        </is>
+      </c>
+      <c r="AA639" s="2" t="inlineStr">
+        <is>
+          <t>0.000136</t>
+        </is>
+      </c>
+      <c r="AB639" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC639" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:25:55.901970Z</t>
+        </is>
+      </c>
       <c r="AD639" s="2" t="inlineStr"/>
       <c r="AE639" s="2" t="inlineStr"/>
       <c r="AF639" s="2" t="inlineStr"/>
@@ -72050,14 +72070,34 @@
       <c r="W654" s="2" t="inlineStr"/>
       <c r="X654" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y654" s="2" t="inlineStr"/>
-      <c r="Z654" s="2" t="inlineStr"/>
-      <c r="AA654" s="2" t="inlineStr"/>
-      <c r="AB654" s="2" t="inlineStr"/>
-      <c r="AC654" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y654" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z654" s="2" t="inlineStr">
+        <is>
+          <t>0.840000</t>
+        </is>
+      </c>
+      <c r="AA654" s="2" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="AB654" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC654" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:25:58.594675Z</t>
+        </is>
+      </c>
       <c r="AD654" s="2" t="inlineStr"/>
       <c r="AE654" s="2" t="inlineStr"/>
       <c r="AF654" s="2" t="inlineStr"/>
@@ -73444,8 +73484,856 @@
       <c r="AI667" s="2" t="inlineStr"/>
       <c r="AJ667" s="2" t="inlineStr"/>
     </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>6870d827f402494a</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182209</t>
+        </is>
+      </c>
+      <c r="I668" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J668" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K668" s="2" t="inlineStr"/>
+      <c r="L668" s="2" t="inlineStr">
+        <is>
+          <t>0.502257</t>
+        </is>
+      </c>
+      <c r="M668" s="2" t="inlineStr"/>
+      <c r="N668" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O668" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P668" s="2" t="inlineStr"/>
+      <c r="Q668" s="2" t="inlineStr">
+        <is>
+          <t>-0.21763095518207287</t>
+        </is>
+      </c>
+      <c r="R668" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:08.001910Z</t>
+        </is>
+      </c>
+      <c r="S668" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00Z</t>
+        </is>
+      </c>
+      <c r="T668" s="2" t="inlineStr"/>
+      <c r="U668" s="2" t="inlineStr"/>
+      <c r="V668" s="2" t="inlineStr"/>
+      <c r="W668" s="2" t="inlineStr"/>
+      <c r="X668" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y668" s="2" t="inlineStr"/>
+      <c r="Z668" s="2" t="inlineStr"/>
+      <c r="AA668" s="2" t="inlineStr"/>
+      <c r="AB668" s="2" t="inlineStr"/>
+      <c r="AC668" s="2" t="inlineStr"/>
+      <c r="AD668" s="2" t="inlineStr"/>
+      <c r="AE668" s="2" t="inlineStr"/>
+      <c r="AF668" s="2" t="inlineStr"/>
+      <c r="AG668" s="2" t="inlineStr"/>
+      <c r="AH668" s="2" t="inlineStr"/>
+      <c r="AI668" s="2" t="inlineStr"/>
+      <c r="AJ668" s="2" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>0d6bc417fded4d60</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182205</t>
+        </is>
+      </c>
+      <c r="I669" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J669" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K669" s="2" t="inlineStr"/>
+      <c r="L669" s="2" t="inlineStr">
+        <is>
+          <t>0.633161</t>
+        </is>
+      </c>
+      <c r="M669" s="2" t="inlineStr"/>
+      <c r="N669" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O669" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P669" s="2" t="inlineStr"/>
+      <c r="Q669" s="2" t="inlineStr">
+        <is>
+          <t>-0.05724147678018576</t>
+        </is>
+      </c>
+      <c r="R669" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:08.316689Z</t>
+        </is>
+      </c>
+      <c r="S669" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00Z</t>
+        </is>
+      </c>
+      <c r="T669" s="2" t="inlineStr"/>
+      <c r="U669" s="2" t="inlineStr"/>
+      <c r="V669" s="2" t="inlineStr"/>
+      <c r="W669" s="2" t="inlineStr"/>
+      <c r="X669" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y669" s="2" t="inlineStr"/>
+      <c r="Z669" s="2" t="inlineStr"/>
+      <c r="AA669" s="2" t="inlineStr"/>
+      <c r="AB669" s="2" t="inlineStr"/>
+      <c r="AC669" s="2" t="inlineStr"/>
+      <c r="AD669" s="2" t="inlineStr"/>
+      <c r="AE669" s="2" t="inlineStr"/>
+      <c r="AF669" s="2" t="inlineStr"/>
+      <c r="AG669" s="2" t="inlineStr"/>
+      <c r="AH669" s="2" t="inlineStr"/>
+      <c r="AI669" s="2" t="inlineStr"/>
+      <c r="AJ669" s="2" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>7cc8c887a8074529</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182212</t>
+        </is>
+      </c>
+      <c r="I670" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K670" s="2" t="inlineStr"/>
+      <c r="L670" s="2" t="inlineStr">
+        <is>
+          <t>0.67718</t>
+        </is>
+      </c>
+      <c r="M670" s="2" t="inlineStr"/>
+      <c r="N670" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O670" s="2" t="inlineStr">
+        <is>
+          <t>0.7297297297297298</t>
+        </is>
+      </c>
+      <c r="P670" s="2" t="inlineStr"/>
+      <c r="Q670" s="2" t="inlineStr">
+        <is>
+          <t>-0.05254972972972982</t>
+        </is>
+      </c>
+      <c r="R670" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:06.394719Z</t>
+        </is>
+      </c>
+      <c r="S670" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T22:30Z</t>
+        </is>
+      </c>
+      <c r="T670" s="2" t="inlineStr"/>
+      <c r="U670" s="2" t="inlineStr"/>
+      <c r="V670" s="2" t="inlineStr"/>
+      <c r="W670" s="2" t="inlineStr"/>
+      <c r="X670" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y670" s="2" t="inlineStr"/>
+      <c r="Z670" s="2" t="inlineStr"/>
+      <c r="AA670" s="2" t="inlineStr"/>
+      <c r="AB670" s="2" t="inlineStr"/>
+      <c r="AC670" s="2" t="inlineStr"/>
+      <c r="AD670" s="2" t="inlineStr"/>
+      <c r="AE670" s="2" t="inlineStr"/>
+      <c r="AF670" s="2" t="inlineStr"/>
+      <c r="AG670" s="2" t="inlineStr"/>
+      <c r="AH670" s="2" t="inlineStr"/>
+      <c r="AI670" s="2" t="inlineStr"/>
+      <c r="AJ670" s="2" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>9b6a3fe166894b4d</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182222</t>
+        </is>
+      </c>
+      <c r="I671" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J671" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K671" s="2" t="inlineStr"/>
+      <c r="L671" s="2" t="inlineStr">
+        <is>
+          <t>0.801053</t>
+        </is>
+      </c>
+      <c r="M671" s="2" t="inlineStr"/>
+      <c r="N671" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O671" s="2" t="inlineStr">
+        <is>
+          <t>0.7802197802197802</t>
+        </is>
+      </c>
+      <c r="P671" s="2" t="inlineStr"/>
+      <c r="Q671" s="2" t="inlineStr">
+        <is>
+          <t>0.02083321978021979</t>
+        </is>
+      </c>
+      <c r="R671" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:09.476094Z</t>
+        </is>
+      </c>
+      <c r="S671" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:00Z</t>
+        </is>
+      </c>
+      <c r="T671" s="2" t="inlineStr"/>
+      <c r="U671" s="2" t="inlineStr"/>
+      <c r="V671" s="2" t="inlineStr"/>
+      <c r="W671" s="2" t="inlineStr"/>
+      <c r="X671" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y671" s="2" t="inlineStr"/>
+      <c r="Z671" s="2" t="inlineStr"/>
+      <c r="AA671" s="2" t="inlineStr"/>
+      <c r="AB671" s="2" t="inlineStr"/>
+      <c r="AC671" s="2" t="inlineStr"/>
+      <c r="AD671" s="2" t="inlineStr"/>
+      <c r="AE671" s="2" t="inlineStr"/>
+      <c r="AF671" s="2" t="inlineStr"/>
+      <c r="AG671" s="2" t="inlineStr"/>
+      <c r="AH671" s="2" t="inlineStr"/>
+      <c r="AI671" s="2" t="inlineStr"/>
+      <c r="AJ671" s="2" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>0ca3adf1ccc14be7</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181777</t>
+        </is>
+      </c>
+      <c r="I672" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J672" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K672" s="2" t="inlineStr"/>
+      <c r="L672" s="2" t="inlineStr">
+        <is>
+          <t>0.706207</t>
+        </is>
+      </c>
+      <c r="M672" s="2" t="inlineStr"/>
+      <c r="N672" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O672" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P672" s="2" t="inlineStr"/>
+      <c r="Q672" s="2" t="inlineStr">
+        <is>
+          <t>0.03624000330033006</t>
+        </is>
+      </c>
+      <c r="R672" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:14.931621Z</t>
+        </is>
+      </c>
+      <c r="S672" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T22:00Z</t>
+        </is>
+      </c>
+      <c r="T672" s="2" t="inlineStr"/>
+      <c r="U672" s="2" t="inlineStr"/>
+      <c r="V672" s="2" t="inlineStr"/>
+      <c r="W672" s="2" t="inlineStr"/>
+      <c r="X672" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y672" s="2" t="inlineStr"/>
+      <c r="Z672" s="2" t="inlineStr"/>
+      <c r="AA672" s="2" t="inlineStr"/>
+      <c r="AB672" s="2" t="inlineStr"/>
+      <c r="AC672" s="2" t="inlineStr"/>
+      <c r="AD672" s="2" t="inlineStr"/>
+      <c r="AE672" s="2" t="inlineStr"/>
+      <c r="AF672" s="2" t="inlineStr"/>
+      <c r="AG672" s="2" t="inlineStr"/>
+      <c r="AH672" s="2" t="inlineStr"/>
+      <c r="AI672" s="2" t="inlineStr"/>
+      <c r="AJ672" s="2" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>f9a82072165a4785</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181751</t>
+        </is>
+      </c>
+      <c r="I673" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J673" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K673" s="2" t="inlineStr"/>
+      <c r="L673" s="2" t="inlineStr">
+        <is>
+          <t>0.544096</t>
+        </is>
+      </c>
+      <c r="M673" s="2" t="inlineStr"/>
+      <c r="N673" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O673" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P673" s="2" t="inlineStr"/>
+      <c r="Q673" s="2" t="inlineStr">
+        <is>
+          <t>-0.0054535495495494635</t>
+        </is>
+      </c>
+      <c r="R673" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:10.393455Z</t>
+        </is>
+      </c>
+      <c r="S673" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:00Z</t>
+        </is>
+      </c>
+      <c r="T673" s="2" t="inlineStr"/>
+      <c r="U673" s="2" t="inlineStr"/>
+      <c r="V673" s="2" t="inlineStr"/>
+      <c r="W673" s="2" t="inlineStr"/>
+      <c r="X673" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y673" s="2" t="inlineStr"/>
+      <c r="Z673" s="2" t="inlineStr"/>
+      <c r="AA673" s="2" t="inlineStr"/>
+      <c r="AB673" s="2" t="inlineStr"/>
+      <c r="AC673" s="2" t="inlineStr"/>
+      <c r="AD673" s="2" t="inlineStr"/>
+      <c r="AE673" s="2" t="inlineStr"/>
+      <c r="AF673" s="2" t="inlineStr"/>
+      <c r="AG673" s="2" t="inlineStr"/>
+      <c r="AH673" s="2" t="inlineStr"/>
+      <c r="AI673" s="2" t="inlineStr"/>
+      <c r="AJ673" s="2" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>515bddc8e34a4a93</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181766</t>
+        </is>
+      </c>
+      <c r="I674" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J674" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K674" s="2" t="inlineStr"/>
+      <c r="L674" s="2" t="inlineStr">
+        <is>
+          <t>0.592411</t>
+        </is>
+      </c>
+      <c r="M674" s="2" t="inlineStr"/>
+      <c r="N674" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O674" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P674" s="2" t="inlineStr"/>
+      <c r="Q674" s="2" t="inlineStr">
+        <is>
+          <t>0.13158150691244241</t>
+        </is>
+      </c>
+      <c r="R674" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:15.652471Z</t>
+        </is>
+      </c>
+      <c r="S674" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:30Z</t>
+        </is>
+      </c>
+      <c r="T674" s="2" t="inlineStr"/>
+      <c r="U674" s="2" t="inlineStr"/>
+      <c r="V674" s="2" t="inlineStr"/>
+      <c r="W674" s="2" t="inlineStr"/>
+      <c r="X674" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y674" s="2" t="inlineStr"/>
+      <c r="Z674" s="2" t="inlineStr"/>
+      <c r="AA674" s="2" t="inlineStr"/>
+      <c r="AB674" s="2" t="inlineStr"/>
+      <c r="AC674" s="2" t="inlineStr"/>
+      <c r="AD674" s="2" t="inlineStr"/>
+      <c r="AE674" s="2" t="inlineStr"/>
+      <c r="AF674" s="2" t="inlineStr"/>
+      <c r="AG674" s="2" t="inlineStr"/>
+      <c r="AH674" s="2" t="inlineStr"/>
+      <c r="AI674" s="2" t="inlineStr"/>
+      <c r="AJ674" s="2" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>3dcd419cf0cd48ef</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181768</t>
+        </is>
+      </c>
+      <c r="I675" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J675" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K675" s="2" t="inlineStr"/>
+      <c r="L675" s="2" t="inlineStr">
+        <is>
+          <t>0.573609</t>
+        </is>
+      </c>
+      <c r="M675" s="2" t="inlineStr"/>
+      <c r="N675" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O675" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P675" s="2" t="inlineStr"/>
+      <c r="Q675" s="2" t="inlineStr">
+        <is>
+          <t>-0.046162863117870656</t>
+        </is>
+      </c>
+      <c r="R675" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:16.728202Z</t>
+        </is>
+      </c>
+      <c r="S675" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T00:30Z</t>
+        </is>
+      </c>
+      <c r="T675" s="2" t="inlineStr"/>
+      <c r="U675" s="2" t="inlineStr"/>
+      <c r="V675" s="2" t="inlineStr"/>
+      <c r="W675" s="2" t="inlineStr"/>
+      <c r="X675" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y675" s="2" t="inlineStr"/>
+      <c r="Z675" s="2" t="inlineStr"/>
+      <c r="AA675" s="2" t="inlineStr"/>
+      <c r="AB675" s="2" t="inlineStr"/>
+      <c r="AC675" s="2" t="inlineStr"/>
+      <c r="AD675" s="2" t="inlineStr"/>
+      <c r="AE675" s="2" t="inlineStr"/>
+      <c r="AF675" s="2" t="inlineStr"/>
+      <c r="AG675" s="2" t="inlineStr"/>
+      <c r="AH675" s="2" t="inlineStr"/>
+      <c r="AI675" s="2" t="inlineStr"/>
+      <c r="AJ675" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ667"/>
+  <autoFilter ref="A1:AJ675"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>